--- a/Diccionario_SenecaféAlpes.xlsx
+++ b/Diccionario_SenecaféAlpes.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\dell\Documents\Uniandes\Cursos_2025_20\IN\Laboratorios\Agrupación\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniandes-my.sharepoint.com/personal/w_bayona_uniandes_edu_co/Documents/College/10. Tenth Semester Stuff/BI/Lab2-BI/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17CA8570-4269-4C98-8ADC-C1F83E5612BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{912237B1-D28C-43F6-A85F-65AB1CB388A1}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{912237B1-D28C-43F6-A85F-65AB1CB388A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -553,14 +553,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0F48892-3FFD-4484-A042-98E6149BE8CF}">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.5703125" customWidth="1"/>
-    <col min="2" max="2" width="165.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" customWidth="1"/>
+    <col min="1" max="1" width="23.5546875" customWidth="1"/>
+    <col min="2" max="2" width="165.6640625" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -568,7 +568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>33</v>
       </c>
@@ -576,7 +576,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -584,7 +584,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -592,7 +592,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
@@ -600,7 +600,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -608,7 +608,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -616,7 +616,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -624,7 +624,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -632,7 +632,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -640,7 +640,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
@@ -648,7 +648,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
@@ -656,7 +656,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
@@ -664,7 +664,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
@@ -672,7 +672,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
@@ -680,7 +680,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
@@ -688,7 +688,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
@@ -696,7 +696,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
@@ -704,7 +704,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>35</v>
       </c>
@@ -712,7 +712,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>36</v>
       </c>
